--- a/doc/导入课程任务测试数据高一12345班-65条编码.xlsx
+++ b/doc/导入课程任务测试数据高一12345班-65条编码.xlsx
@@ -249,6 +249,97 @@
     <t>42</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>0</t>
+    </r>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20200</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>01</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10003</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <t>高一数学必修1</t>
+  </si>
+  <si>
+    <t>李雪雪</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -260,8 +351,29 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2</t>
-    </r>
+      <t>2020010</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>100056</t>
+  </si>
+  <si>
+    <t>高一英语必修1</t>
+  </si>
+  <si>
+    <t>王小芳</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -272,9 +384,61 @@
       </rPr>
       <t>0</t>
     </r>
-  </si>
-  <si>
-    <t>1</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1</t>
+    </r>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>100004</t>
+  </si>
+  <si>
+    <t>高一物理1</t>
+  </si>
+  <si>
+    <t>张德良</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>100014</t>
+  </si>
+  <si>
+    <t>高一化学必修1</t>
+  </si>
+  <si>
+    <t>韩云</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>100041</t>
+  </si>
+  <si>
+    <t>高一思想政治必修1</t>
+  </si>
+  <si>
+    <t>江大波</t>
+  </si>
+  <si>
+    <t>100021</t>
+  </si>
+  <si>
+    <t>高一历史必修1</t>
+  </si>
+  <si>
+    <t>吴天盛</t>
   </si>
   <si>
     <r>
@@ -295,6 +459,51 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
+      <t>101</t>
+    </r>
+  </si>
+  <si>
+    <t>100007</t>
+  </si>
+  <si>
+    <t>高一地理必修1</t>
+  </si>
+  <si>
+    <t>王杰</t>
+  </si>
+  <si>
+    <t>100027</t>
+  </si>
+  <si>
+    <t>高一生物必修1：分子与细胞</t>
+  </si>
+  <si>
+    <t>谭咏麟</t>
+  </si>
+  <si>
+    <t>100051</t>
+  </si>
+  <si>
+    <t>体育课</t>
+  </si>
+  <si>
+    <t>张杰</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>1</t>
     </r>
     <r>
@@ -305,215 +514,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>01</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10003</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3</t>
-    </r>
-  </si>
-  <si>
-    <t>高一数学必修1</t>
-  </si>
-  <si>
-    <t>李雪雪</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2020010</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>100056</t>
-  </si>
-  <si>
-    <t>高一英语必修1</t>
-  </si>
-  <si>
-    <t>王小芳</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>100004</t>
-  </si>
-  <si>
-    <t>高一物理1</t>
-  </si>
-  <si>
-    <t>张德良</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>100014</t>
-  </si>
-  <si>
-    <t>高一化学必修1</t>
-  </si>
-  <si>
-    <t>韩云</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>100041</t>
-  </si>
-  <si>
-    <t>高一思想政治必修1</t>
-  </si>
-  <si>
-    <t>江大波</t>
-  </si>
-  <si>
-    <t>100021</t>
-  </si>
-  <si>
-    <t>高一历史必修1</t>
-  </si>
-  <si>
-    <t>吴天盛</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>20200</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>101</t>
-    </r>
-  </si>
-  <si>
-    <t>100007</t>
-  </si>
-  <si>
-    <t>高一地理必修1</t>
-  </si>
-  <si>
-    <t>王杰</t>
-  </si>
-  <si>
-    <t>100027</t>
-  </si>
-  <si>
-    <t>高一生物必修1：分子与细胞</t>
-  </si>
-  <si>
-    <t>谭咏麟</t>
-  </si>
-  <si>
-    <t>100051</t>
-  </si>
-  <si>
-    <t>体育课</t>
-  </si>
-  <si>
-    <t>张杰</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>4</t>
     </r>
   </si>
@@ -527,7 +527,7 @@
     <t>03</t>
   </si>
   <si>
-    <t>05</t>
+    <t>1521</t>
   </si>
   <si>
     <r>
@@ -2947,7 +2947,7 @@
         <v>27</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K4" s="3" t="s">
         <v>21</v>
@@ -2964,28 +2964,28 @@
         <v>15</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>10013</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>21</v>
@@ -3005,25 +3005,25 @@
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F6">
         <v>10025</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>21</v>
@@ -3043,25 +3043,25 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>10033</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K7" s="3" t="s">
         <v>21</v>
@@ -3075,7 +3075,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>16</v>
@@ -3093,13 +3093,13 @@
         <v>45</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>21</v>
@@ -3113,7 +3113,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -3131,13 +3131,13 @@
         <v>48</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>21</v>
@@ -3169,13 +3169,13 @@
         <v>52</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>21</v>
@@ -3207,13 +3207,13 @@
         <v>55</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K11" s="3" t="s">
         <v>21</v>
@@ -3248,7 +3248,7 @@
         <v>59</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>60</v>
@@ -3283,16 +3283,16 @@
         <v>10025</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>64</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K13" s="3" t="s">
         <v>21</v>
@@ -3309,7 +3309,7 @@
         <v>66</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>16</v>
@@ -3374,7 +3374,7 @@
         <v>19</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>21</v>
@@ -3412,7 +3412,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>21</v>
@@ -3432,25 +3432,25 @@
         <v>73</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F17">
         <v>10013</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>21</v>
@@ -3470,19 +3470,19 @@
         <v>73</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18">
         <v>10025</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>19</v>
@@ -3508,22 +3508,22 @@
         <v>73</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F19">
         <v>10033</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>60</v>
@@ -3540,7 +3540,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>73</v>
@@ -3558,13 +3558,13 @@
         <v>45</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>21</v>
@@ -3578,7 +3578,7 @@
         <v>14</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>73</v>
@@ -3596,13 +3596,13 @@
         <v>48</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>21</v>
@@ -3634,13 +3634,13 @@
         <v>52</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>21</v>
@@ -3672,10 +3672,10 @@
         <v>55</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>60</v>
@@ -3713,7 +3713,7 @@
         <v>59</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>60</v>
@@ -3748,13 +3748,13 @@
         <v>10025</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>64</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J25" s="3" t="s">
         <v>60</v>
@@ -3774,7 +3774,7 @@
         <v>66</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>76</v>
@@ -3833,13 +3833,13 @@
         <v>80</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>21</v>
@@ -3871,13 +3871,13 @@
         <v>84</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>21</v>
@@ -3900,7 +3900,7 @@
         <v>85</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F29">
         <v>10029</v>
@@ -3909,13 +3909,13 @@
         <v>86</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>21</v>
@@ -3938,13 +3938,13 @@
         <v>87</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F30">
         <v>10025</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>88</v>
@@ -3953,7 +3953,7 @@
         <v>81</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>21</v>
@@ -3991,7 +3991,7 @@
         <v>81</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K31" s="3" t="s">
         <v>21</v>
@@ -4005,7 +4005,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>78</v>
@@ -4029,7 +4029,7 @@
         <v>81</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>21</v>
@@ -4043,7 +4043,7 @@
         <v>14</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>78</v>
@@ -4237,7 +4237,7 @@
         <v>66</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>78</v>
@@ -4252,7 +4252,7 @@
         <v>10025</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>70</v>
@@ -4275,7 +4275,7 @@
         <v>14</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>78</v>
@@ -4331,13 +4331,13 @@
         <v>86</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K40" s="3" t="s">
         <v>112</v>
@@ -4351,7 +4351,7 @@
         <v>14</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>111</v>
@@ -4366,16 +4366,16 @@
         <v>10033</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>113</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>112</v>
@@ -4398,7 +4398,7 @@
         <v>85</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F42">
         <v>10020</v>
@@ -4407,13 +4407,13 @@
         <v>114</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>113</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>112</v>
@@ -4436,7 +4436,7 @@
         <v>87</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F43">
         <v>10035</v>
@@ -4451,7 +4451,7 @@
         <v>113</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K43" s="3" t="s">
         <v>112</v>
@@ -4489,7 +4489,7 @@
         <v>113</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K44" s="3" t="s">
         <v>112</v>
@@ -4527,7 +4527,7 @@
         <v>113</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K45" s="3" t="s">
         <v>112</v>
@@ -4565,7 +4565,7 @@
         <v>113</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>112</v>
@@ -4579,7 +4579,7 @@
         <v>14</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>111</v>
@@ -4603,7 +4603,7 @@
         <v>113</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>112</v>
@@ -4617,7 +4617,7 @@
         <v>14</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>111</v>
@@ -4641,7 +4641,7 @@
         <v>113</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K48" s="3" t="s">
         <v>112</v>
@@ -4746,7 +4746,7 @@
         <v>10025</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>70</v>
@@ -4825,13 +4825,13 @@
         <v>86</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I53" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K53" s="3" t="s">
         <v>112</v>
@@ -4845,7 +4845,7 @@
         <v>14</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>115</v>
@@ -4860,16 +4860,16 @@
         <v>10033</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>113</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>112</v>
@@ -4892,7 +4892,7 @@
         <v>85</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F55">
         <v>10020</v>
@@ -4901,13 +4901,13 @@
         <v>114</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I55" s="3" t="s">
         <v>113</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="K55" s="3" t="s">
         <v>112</v>
@@ -4930,7 +4930,7 @@
         <v>87</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F56">
         <v>10035</v>
@@ -4945,7 +4945,7 @@
         <v>113</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>112</v>
@@ -4983,7 +4983,7 @@
         <v>113</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K57" s="3" t="s">
         <v>112</v>
@@ -5021,7 +5021,7 @@
         <v>113</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>112</v>
@@ -5059,7 +5059,7 @@
         <v>113</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>112</v>
@@ -5073,7 +5073,7 @@
         <v>14</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>115</v>
@@ -5097,7 +5097,7 @@
         <v>113</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>112</v>
@@ -5111,7 +5111,7 @@
         <v>66</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>115</v>
@@ -5135,7 +5135,7 @@
         <v>113</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="K61" s="3" t="s">
         <v>112</v>
@@ -5240,7 +5240,7 @@
         <v>10025</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>70</v>
